--- a/jobsy_reference_library.xlsx
+++ b/jobsy_reference_library.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4264,6 +4264,706 @@
         </is>
       </c>
       <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>J-EXEC-02</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Chief Technology Officer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Leadership &amp; Management</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>13</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Managing directors and chief executives</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>chief technology officer</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>J-EXEC-03</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Leadership &amp; Management</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>13</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Managing directors and chief executives</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>chief operating officer</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>J-EXEC-04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Leadership &amp; Management</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>13</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Managing directors and chief executives</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>chief financial officer</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>J-EXEC-05</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chief Human Resources Officer</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Leadership &amp; Management</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>13</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Managing directors and chief executives</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>chief human resources officer</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>J-EXEC-06</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Chief Marketing Officer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Leadership &amp; Management</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>13</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Managing directors and chief executives</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>chief marketing officer</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>J-EXEC-07</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Chief Commercial Officer</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Leadership &amp; Management</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>13</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Managing directors and chief executives</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>chief commercial officer</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>J-EXEC-08</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Chief Product Officer</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Leadership &amp; Management</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>13</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Managing directors and chief executives</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>chief product officer</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>J-EXEC-09</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Chief Data Officer</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Leadership &amp; Management</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>13</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Managing directors and chief executives</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>chief data officer</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Leadership &amp; Management</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>13</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Managing directors and chief executives</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>chief information officer</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>J-EXEC-11</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Chief Legal Officer</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Leadership &amp; Management</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>13</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Managing directors and chief executives</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>chief legal officer</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -4543,7 +5243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I362"/>
+  <dimension ref="A1:I443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20839,6 +21539,3651 @@
         </is>
       </c>
       <c r="I362" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>J-EXEC-02</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>SK-PRO-01</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>3</v>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>J-EXEC-02</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>SK-TECH-09</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>3</v>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>J-EXEC-02</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>SK-LDR-01</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>4</v>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>J-EXEC-02</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>SK-LDR-06</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>4</v>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>J-EXEC-02</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>SK-LDR-07</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>4</v>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>J-EXEC-02</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>SK-TECH-08</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>4</v>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>J-EXEC-02</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>SK-LDR-02</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>4</v>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>J-EXEC-02</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SK-LDR-03</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>4</v>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>J-EXEC-02</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>SK-LDR-09</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>3</v>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>J-EXEC-03</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>SK-LDR-08</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>4</v>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>J-EXEC-03</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>SK-PRO-02</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>4</v>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>J-EXEC-03</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>SK-LDR-01</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>4</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>J-EXEC-03</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SK-LDR-06</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>5</v>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>J-EXEC-03</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>SK-LDR-09</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>5</v>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>J-EXEC-03</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>SK-PRO-03</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>4</v>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>J-EXEC-03</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>SK-LDR-04</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>4</v>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>J-EXEC-03</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>SK-LDR-05</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>4</v>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>J-EXEC-04</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>SK-LDR-09</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>5</v>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>J-EXEC-04</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>SK-PRO-03</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>4</v>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>J-EXEC-04</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>SK-FIN-04</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>5</v>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>J-EXEC-04</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>SK-FIN-07</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>5</v>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>J-EXEC-04</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SK-LDR-06</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>5</v>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>J-EXEC-04</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>SK-LDR-08</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>4</v>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>J-EXEC-04</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>SK-LDR-01</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>4</v>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>J-EXEC-04</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>SK-LDR-04</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>4</v>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>J-EXEC-05</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>SK-LDR-05</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>4</v>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>J-EXEC-05</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>SK-LDR-08</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>4</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>J-EXEC-05</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>SK-PRO-03</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>4</v>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>J-EXEC-05</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>SK-HR-02</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>5</v>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>J-EXEC-05</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>SK-HR-04</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>5</v>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>J-EXEC-05</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>SK-LDR-01</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>5</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>J-EXEC-05</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>SK-LDR-06</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>5</v>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>J-EXEC-05</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>SK-HR-03</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>4</v>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>J-EXEC-05</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>SK-LDR-09</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>4</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>J-EXEC-06</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>SK-LDR-08</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>4</v>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>J-EXEC-06</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>SK-LDR-09</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>4</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>J-EXEC-06</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>SK-COM-05</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>4</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>J-EXEC-06</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>SK-LDR-01</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>4</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>J-EXEC-06</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>SK-LDR-06</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>5</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>J-EXEC-06</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>SK-MKT-05</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>5</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>J-EXEC-06</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>SK-LDR-02</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>4</v>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>J-EXEC-06</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>SK-LDR-04</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>4</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>J-EXEC-07</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>SK-LDR-08</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>4</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>J-EXEC-07</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>SK-LDR-09</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>4</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>J-EXEC-07</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>SK-COM-05</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>4</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>J-EXEC-07</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>SK-COM-06</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>5</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>J-EXEC-07</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>SK-LDR-01</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>4</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>J-EXEC-07</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>SK-LDR-06</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>4</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>J-EXEC-07</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>SK-LDR-02</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>4</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>J-EXEC-08</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>SK-PRO-05</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>4</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>J-EXEC-08</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>SK-COM-05</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>4</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>J-EXEC-08</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>SK-LDR-01</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>5</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>J-EXEC-08</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>SK-LDR-06</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>5</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>J-EXEC-08</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>SK-LDR-08</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>4</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>J-EXEC-08</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>SK-LDR-02</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>4</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>J-EXEC-08</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>SK-LDR-09</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>5</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>J-EXEC-09</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>SK-DATA-04</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>4</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>J-EXEC-09</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>SK-LDR-08</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>4</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>J-EXEC-09</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>SK-PRO-07</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>4</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>J-EXEC-09</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>SK-DATA-09</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>5</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>J-EXEC-09</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>SK-LDR-01</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>4</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>J-EXEC-09</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>SK-LDR-06</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>5</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>J-EXEC-09</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>SK-LDR-03</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>4</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>J-EXEC-09</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>SK-LDR-09</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>4</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>SK-PRO-01</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>3</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>SK-TECH-09</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>3</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>SK-LDR-01</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>4</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>SK-LDR-06</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>4</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>SK-LDR-07</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>4</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>SK-TECH-08</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>4</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>SK-LDR-02</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>4</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>SK-LDR-03</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>4</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>SK-LDR-09</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>3</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>J-EXEC-11</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>SK-LDR-09</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>4</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>J-EXEC-11</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>SK-PRO-03</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>4</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>J-EXEC-11</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>SK-LDR-06</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>4</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>J-EXEC-11</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>SK-LDR-08</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>5</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>J-EXEC-11</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>SK-PRO-07</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>4</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>J-EXEC-11</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>SK-PRO-08</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>5</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>J-EXEC-11</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>SK-LDR-01</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>4</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>J-EXEC-11</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>SK-LDR-03</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>4</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -30823,7 +35168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -34116,6 +38461,626 @@
         </is>
       </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>J-EXEC-02</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Owns the company's technology vision, architecture and engineering organisation; sets technical strategy and scales the platform and teams.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Set technology strategy and architecture; Build and lead the engineering organisation; Own platform scalability, security and reliability; Advise the CEO and board on technology investment; Drive technical hiring and engineering culture</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Technology strategy; Engineering leadership; System architecture; Scaling teams; Security and reliability</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SaaS platforms; Scale-up engineering; Cloud architecture</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Executive — C-suite leader of the technology function</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>GitHub; AWS/Azure/GCP; Jira; Datadog; Power BI</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>J-EXEC-03</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Owns company-wide operational strategy and execution; partners with the CEO to scale the business efficiently and reliably across all functions.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Set operational strategy and company-wide execution; Drive efficiency and scalability; Own cross-functional delivery and performance; Partner with the CEO on business continuity; Build and lead the operations leadership team</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Operational strategy; Company-wide execution; Scaling operations; Cross-functional leadership; Performance management</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Company operations; Scale-up leadership; Process excellence</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Executive — C-suite leader of the operating function</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SAP or Oracle; Salesforce; Power BI; Jira; Workday</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>J-EXEC-04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Owns financial strategy, controlling, treasury and investor reporting; accountable for the financial health and integrity of the company.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Set financial strategy and capital allocation; Own controlling, treasury and reporting; Lead budgeting and forecasting; Manage investor and board reporting; Ensure financial controls and compliance</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Financial strategy; Controlling; Treasury; Investor relations; Financial controls</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PE/VC-backed finance; Scale-up finance; M&amp;A</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Executive — C-suite leader of the financial function</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SAP or Oracle; Excel; Power BI; NetSuite; Board portal</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>J-EXEC-05</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Owns people strategy, organisation design, culture and reward; accountable for building the organisation and its leadership capability.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Set people and talent strategy; Own organisation design and culture; Lead reward, performance and succession; Advise the CEO and board on people risk; Build the HR leadership team</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>People strategy; Organisation design; Culture; Reward; Talent and succession</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Scale-up people leadership; Change management; Total reward</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Executive — C-suite leader of the human resources function</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Workday; AFAS; Power BI; Culture Amp; Board portal</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>J-EXEC-06</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Owns marketing, brand and growth strategy; accountable for demand, positioning and the marketing organisation.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Set marketing and brand strategy; Own demand generation and growth; Lead positioning and messaging; Manage marketing budget and ROI; Build the marketing leadership team</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Marketing strategy; Brand; Growth; Demand generation; Positioning</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>B2B growth; Brand building; Digital marketing</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Executive — C-suite leader of the marketing function</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>HubSpot; Google Analytics; Power BI; Salesforce; LinkedIn</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>J-EXEC-07</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Owns commercial and revenue strategy across sales and go-to-market; accountable for revenue growth and the commercial organisation.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Set commercial and revenue strategy; Own sales and go-to-market; Lead pricing and pipeline; Drive revenue growth and forecasting; Build the commercial leadership team</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Commercial strategy; Revenue growth; Go-to-market; Pricing; Sales leadership</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>B2B sales leadership; Revenue operations; Scale-up commercial</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Executive — C-suite leader of the commercial function</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Salesforce; HubSpot; Power BI; Gong; LinkedIn</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>J-EXEC-08</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Owns product vision, strategy and roadmap; accountable for product-market fit and the product organisation.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Set product vision and strategy; Own the roadmap and discovery; Align product with company strategy; Lead prioritisation and outcomes; Build the product leadership team</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Product strategy; Roadmap; Discovery; Prioritisation; Product leadership</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SaaS product; Platform product; Product-led growth</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Executive — C-suite leader of the product function</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Jira; Productboard; Amplitude; Figma; Power BI</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>J-EXEC-09</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Owns data strategy, analytics and governance; accountable for turning data into value and for the data organisation.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Set data and analytics strategy; Own data governance and quality; Lead the data platform and analytics; Advise leadership on data-driven decisions; Build the data leadership team</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Data strategy; Analytics; Data governance; Data platform; Data leadership</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Analytics leadership; Data platform; Data governance</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Executive — C-suite leader of the data function</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Snowflake; dbt; Power BI; Python; Looker</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Owns IT strategy, enterprise systems and information security; accountable for the technology backbone and information risk of the company.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Set IT and systems strategy; Own enterprise systems and infrastructure; Lead information security and risk; Manage IT budget and vendors; Build the IT leadership team</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>IT strategy; Enterprise systems; Infrastructure; Information security; Vendor management</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Enterprise IT; Information security; Systems integration</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Executive — C-suite leader of the information function</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ServiceNow; Microsoft 365; Azure; Okta; Power BI</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>J-EXEC-11</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Owns legal strategy, governance, compliance and risk; accountable for protecting the company legally and for the legal organisation.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Set legal and governance strategy; Own compliance and risk; Lead contracts and corporate legal; Advise the CEO and board on legal risk; Build the legal team</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Legal strategy; Governance; Compliance; Risk; Corporate legal</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Corporate law; Compliance; Data protection</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Executive — C-suite leader of the legal function</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>iManage; DocuSign; Board portal; OneTrust; Excel</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -40741,7 +45706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -41385,7 +46350,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>J-HR-05</t>
+          <t>J-EXEC-05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -42014,7 +46979,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>J-FIN-06</t>
+          <t>J-EXEC-04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -42458,7 +47423,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>J-ENG-04</t>
+          <t>J-EXEC-02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -43457,7 +48422,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>J-OPS-05</t>
+          <t>J-EXEC-03</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -43938,7 +48903,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>J-SAL-05</t>
+          <t>J-EXEC-07</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -44271,7 +49236,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>J-MKT-05</t>
+          <t>J-EXEC-06</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -44752,7 +49717,7 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>J-FIN-06</t>
+          <t>J-EXEC-04</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -44789,7 +49754,7 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>J-ENG-04</t>
+          <t>J-EXEC-02</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -44826,7 +49791,7 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>J-HR-05</t>
+          <t>J-EXEC-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -44974,7 +49939,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>J-SAL-05</t>
+          <t>J-EXEC-07</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -45011,7 +49976,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>J-SAL-05</t>
+          <t>J-EXEC-07</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -45048,7 +50013,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>J-OPS-05</t>
+          <t>J-EXEC-03</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -45085,7 +50050,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>J-MKT-05</t>
+          <t>J-EXEC-06</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -45122,7 +50087,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>J-PRD-04</t>
+          <t>J-EXEC-08</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -45159,7 +50124,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>J-ENG-04</t>
+          <t>J-EXEC-10</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -45196,7 +50161,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>J-DAT-05</t>
+          <t>J-EXEC-09</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -45233,7 +50198,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>J-LEG-03</t>
+          <t>J-EXEC-11</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -45270,7 +50235,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>J-HR-05</t>
+          <t>J-EXEC-05</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -47477,6 +52442,228 @@
         </is>
       </c>
       <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>CIO</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>CDO</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>J-EXEC-09</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>CPO</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>J-EXEC-08</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>CRO</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>J-EXEC-07</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>CLO</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>J-EXEC-11</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Chief Information Officer (CIO)</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -47494,7 +52681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -49681,6 +54868,426 @@
         </is>
       </c>
       <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>J-EXEC-02</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>J-EXEC-01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>J-EXEC-03</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>J-EXEC-01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>J-EXEC-04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>J-EXEC-01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>J-EXEC-05</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>J-EXEC-01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>J-EXEC-06</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>J-EXEC-01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>J-EXEC-07</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>J-EXEC-01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>J-EXEC-08</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>J-EXEC-01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>J-EXEC-09</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>J-EXEC-01</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>J-EXEC-10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>J-EXEC-01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>J-EXEC-11</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>J-EXEC-01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Seed v1 (exec tier)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>

--- a/jobsy_reference_library.xlsx
+++ b/jobsy_reference_library.xlsx
@@ -52122,7 +52122,7 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>J-FIN-05</t>
+          <t>J-FIN-06</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -52418,7 +52418,7 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>J-MKT-03</t>
+          <t>J-MKT-05</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">

--- a/jobsy_reference_library.xlsx
+++ b/jobsy_reference_library.xlsx
@@ -45706,7 +45706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -52664,6 +52664,191 @@
         </is>
       </c>
       <c r="G188" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Financieel Directeur</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>J-FIN-06</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Seed v1 (nl)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Financieel Manager</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>J-FIN-05</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Seed v1 (nl)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Senior Developer</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>J-ENG-03</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Seed v1 (nl)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Software Ontwikkelaar</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>J-ENG-02</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Seed v1 (nl)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Directeur Operations</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>J-OPS-05</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Seed v1 (nl)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>

--- a/jobsy_reference_library.xlsx
+++ b/jobsy_reference_library.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4964,6 +4964,76 @@
         </is>
       </c>
       <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Product Designer</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Product &amp; Design</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>6</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2166</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Graphic and multimedia designers</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>user experience designer</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -5243,7 +5313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I443"/>
+  <dimension ref="A1:I449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25184,6 +25254,276 @@
         </is>
       </c>
       <c r="I443" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>SK-DATA-01</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>2</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>SK-LDR-07</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>2</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>SK-PRO-05</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>2</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>SK-PRO-01</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>2</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>SK-PRO-04</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>2</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>SK-PRO-09</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>2</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Talent &amp; Capability</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -35168,7 +35508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39081,6 +39421,68 @@
         </is>
       </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Designs intuitive, accessible product experiences end to end — from user research and flows to high-fidelity UI — in close partnership with product and engineering.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Run user research and usability testing; Design flows, wireframes and high-fidelity UI; Build and maintain the design system; Partner with product and engineering on delivery; Advocate for accessibility and UX quality</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>User research; Interaction design; Visual/UI design; Prototyping; Design systems</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SaaS product design; Design systems; UX research</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Individual Contributor</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Figma; FigJam; Maze; Miro; Notion</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -43512,7 +43914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -45689,6 +46091,66 @@
         </is>
       </c>
       <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F37" t="n">
+        <v>68000</v>
+      </c>
+      <c r="G37" t="n">
+        <v>76000</v>
+      </c>
+      <c r="H37" t="n">
+        <v>84000</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -45706,7 +46168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -52849,6 +53311,1153 @@
         </is>
       </c>
       <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Medewerker Financiële Administratie</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>J-FIN-01</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Commercieel Medewerker</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>J-SAL-01</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>People Operations Manager</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>J-HR-04</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Marketing Medewerker</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>J-MKT-01</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Verkoper</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>J-SAL-02</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Projectleider</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>J-OPS-02</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Systeembeheerder</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>J-ENG-05</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Salarisadministrateur</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>J-FIN-01</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Data Analist</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>J-DAT-01</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Werving en Selectie</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>J-HR-06</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>HR Adviseur</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>J-HR-02</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Bedrijfsjurist</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>J-LEG-01</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>J-ENG-02</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>BDM</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>J-SAL-04</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>J-SAL-02</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>J-SAL-02</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>J-ENG-02</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Fullstack Developer</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>J-ENG-02</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Financial Accountant</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>J-FIN-02</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>J-ENG-05</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>SRE</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>J-ENG-05</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Talent Partner</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>J-HR-06</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>J-DAT-03</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Seed v1 (batch2)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>UX Designer</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>UI Designer</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>UX/UI Designer</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Product Designer</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Interaction Designer</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Visual Designer</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Productontwerper</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Digital Designer</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -52866,7 +54475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -55473,6 +57082,48 @@
         </is>
       </c>
       <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>J-PRD-05</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>J-PRD-02</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Seed v1 (design)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Job Architecture</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>

--- a/jobsy_reference_library.xlsx
+++ b/jobsy_reference_library.xlsx
@@ -46168,7 +46168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G224"/>
+  <dimension ref="A1:G245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -54458,6 +54458,783 @@
         </is>
       </c>
       <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Sr Recruiter</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>J-HR-07</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Senior Talent Acquisition Specialist</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>J-HR-07</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Lead Recruiter</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>J-HR-07</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Sr Data Analyst</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>J-DAT-02</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Lead Data Analyst</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>J-DAT-02</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Senior BI Analyst</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>J-DAT-02</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Data Lead</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>J-DAT-05</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Head of Analytics</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>J-DAT-05</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Analytics Lead</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>J-DAT-05</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Hoofd Data</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>J-DAT-05</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>APM</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>J-PRD-01</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Associate PM</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>J-PRD-01</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Junior Product Manager</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>J-PRD-01</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Product Analyst</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>J-PRD-01</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Programme Manager</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>J-OPS-04</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>J-OPS-04</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>TPM</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>J-OPS-04</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Senior Program Manager</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>J-OPS-04</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Senior CSM</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>J-CS-03</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Sr Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>J-CS-03</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Lead Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>J-CS-03</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Seed v1 (dq)</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>

--- a/jobsy_reference_library.xlsx
+++ b/jobsy_reference_library.xlsx
@@ -27,6 +27,7 @@
     <sheet name="SeniorityLevels" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="SkillProficiency" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="DataDictionary" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="SalarySources" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$E$52</definedName>
@@ -35968,7 +35969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39215,6 +39216,1286 @@
       <c r="H81" t="inlineStr">
         <is>
           <t>2026-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>IND-FIN</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>IND-TECH</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>IND-HLTH</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>IND-RET</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>IND-PUB</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>IND-PSV</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>IND-LOG</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>IND-FIN</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>IND-TECH</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>IND-HLTH</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>IND-RET</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>IND-PUB</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>IND-PSV</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>IND-LOG</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>IND-FIN</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>IND-TECH</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>IND-HLTH</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>IND-RET</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>IND-PUB</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>IND-PSV</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>IND-LOG</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>IND-FIN</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>IND-TECH</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>IND-HLTH</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>IND-RET</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>IND-PUB</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>IND-PSV</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>IND-LOG</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Calibrated to CBS bedrijfstak wages 2024 + RobertHalf/RobertWalters NL 2026</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -51819,6 +53100,268 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Publisher</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>AccessedOn</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>Informs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jaarloon werknemers per bedrijfstak</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CBS (Statistics NL)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Official statistics</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.cbs.nl/nl-nl/visualisaties/dashboard-arbeidsmarkt/ontwikkeling-cao-lonen/jaarloon-werknemers-per-bedrijfstak</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Per-industry average wage levels (industry pay index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cao-lonen stijgen in 2025 met 5,0 procent</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CBS (Statistics NL)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Official statistics</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.cbs.nl/nl-nl/nieuws/2026/01/cao-lonen-stijgen-in-2025-met-5-0-procent</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Collective-wage growth by sector (freshness)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Netherlands Salary Guide 2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Robert Half</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Salary guide</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.roberthalf.com/nl/en/insights/salary-guide</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Role benchmarks: finance, IT, admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Salary Survey Netherlands 2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Robert Walters</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Salary guide</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.robertwalters.nl/en/our-services/salary-survey.html</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Role/industry salary ranges</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Structure of earnings by NACE sector</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Eurostat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Official statistics</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/statistics-explained/index.php/Structure_of_earnings_survey</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>EU sector earnings cross-check</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Average Salary in the Netherlands 2026 (sector &amp; role)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Published NL market overviews</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Market overview</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://employsome.com/hire/netherlands/average-salary-netherlands/</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>National average (~EUR 48-53k) + role anchors</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>METHOD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Industry-level pay factors are calibrated to CBS sector wage relativities and public NL salary guides (2026). Function-within-industry tilts are informed estimates. Factors multiply the baseline SalaryBands.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/jobsy_reference_library.xlsx
+++ b/jobsy_reference_library.xlsx
@@ -28,6 +28,8 @@
     <sheet name="SkillProficiency" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="DataDictionary" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="SalarySources" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="PayElements" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="PayMix" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$E$52</definedName>
@@ -53352,10 +53354,3030 @@
           <t>Industry-level pay factors are calibrated to CBS sector wage relativities and public NL salary guides (2026). Function-within-industry tilts are informed estimates. Factors multiply the baseline SalaryBands.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="64" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>ElementID</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>TypicalValue</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>StatutoryNL</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>Taxable</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="J1" s="20" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="K1" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="20" t="inlineStr">
+        <is>
+          <t>EffectiveFrom</t>
+        </is>
+      </c>
+      <c r="M1" s="20" t="inlineStr">
+        <is>
+          <t>UpdatedAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PE-BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Base salary</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fixed cash</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12x monthly</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>100% of pay reference</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No (contractual)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Contractual annual gross base salary — the reference for most other elements.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Seed v1 (pay)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PE-HOL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Holiday allowance (vakantietoeslag)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fixed cash</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>% of base</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes (statutory min 8%)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Statutory 8% holiday allowance, typically paid in May.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Seed v1 (pay)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PE-13</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13th month / year-end</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fixed cash</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>% of base</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8.33% (~1 month)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No (CAO/sector dependent)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Extra month's pay, common across many Dutch sectors and CAOs.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Seed v1 (pay)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PE-VAR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Variable pay / bonus</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Variable cash</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>% of base (on-target)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0-40% by role</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Performance- or target-based bonus/commission; on-target percentage of base.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Seed v1 (pay)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PE-PENS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pension (employer)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Benefits</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>% of pensionable base</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>~10-15% (indicative)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Partly (sector funds)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No (employer cost)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Employer pension contribution; varies by sector fund and scheme.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Seed v1 (pay)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PE-BEN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Benefits &amp; allowances</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Benefits</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fixed / typical</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>varies</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Commute/WFH allowance (~EUR 2.35/day thuiswerkvergoeding), phone, laptop, insurance discounts.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Seed v1 (pay)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PE-LTI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Long-term incentive / equity</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Long-term</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>% or grant (multi-year)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>varies</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Yes (on vest)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Equity, options or long-term cash for senior/executive roles; common in tech scale-ups.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Seed v1 (pay)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>TargetVariablePct</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>ThirteenthMonthPct</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>LTIEligible</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="20" t="inlineStr">
+        <is>
+          <t>EffectiveFrom</t>
+        </is>
+      </c>
+      <c r="K1" s="20" t="inlineStr">
+        <is>
+          <t>UpdatedAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Low or no variable pay.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Low or no variable pay.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Low or no variable pay.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>18</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>35</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Base + annual bonus + long-term incentive; no 13th month.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Low or no variable pay.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Low or no variable pay.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Low or no variable pay.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>18</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>18</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>18</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Modest target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Modest target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>12</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Modest target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>18</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Discretionary/target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>20</v>
+      </c>
+      <c r="D36" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Modest target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Modest target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>12</v>
+      </c>
+      <c r="D38" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Modest target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Modest target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>20</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Modest target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Modest target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>12</v>
+      </c>
+      <c r="D42" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Modest target bonus; grows with seniority.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>15</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Commission-driven; car/mobility typical at senior levels.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>40</v>
+      </c>
+      <c r="D44" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Commission-driven; car/mobility typical at senior levels.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Medior</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>20</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Commission-driven; car/mobility typical at senior levels.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>30</v>
+      </c>
+      <c r="D46" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Commission-driven; car/mobility typical at senior levels.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Calibrated to NL pay-mix norms 2026</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/jobsy_reference_library.xlsx
+++ b/jobsy_reference_library.xlsx
@@ -53108,7 +53108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -53352,6 +53352,38 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>Industry-level pay factors are calibrated to CBS sector wage relativities and public NL salary guides (2026). Function-within-industry tilts are informed estimates. Factors multiply the baseline SalaryBands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Role base-salary validation 2026 (Eng, Data, Finance, Product)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Robert Walters / Robert Half + tech pay aggregators</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Salary guide + aggregators</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.robertwalters.nl/en/our-services/salary-survey.html</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Baseline SalaryBands for senior tech, data, accountant and APM roles</t>
         </is>
       </c>
     </row>
@@ -56787,19 +56819,19 @@
         <v>6</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>42000</v>
+        <v>45000</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>46000</v>
+        <v>49000</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>50000</v>
+        <v>53000</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>54000</v>
+        <v>57000</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>58000</v>
+        <v>62000</v>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
@@ -56808,7 +56840,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Seed v1</t>
+          <t>Validated to NL 2026 market (Robert Walters / Robert Half guides + tech pay aggregators)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -56828,7 +56860,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -57027,19 +57059,19 @@
         <v>6</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>54000</v>
+        <v>55000</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>59000</v>
+        <v>61000</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>64000</v>
+        <v>66000</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>69000</v>
+        <v>71000</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>74000</v>
+        <v>78000</v>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
@@ -57048,7 +57080,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Seed v1</t>
+          <t>Validated to NL 2026 market (Robert Walters / Robert Half guides + tech pay aggregators)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -57068,7 +57100,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -57087,19 +57119,19 @@
         <v>10</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>74000</v>
+        <v>80000</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>80000</v>
+        <v>87000</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>87000</v>
+        <v>95000</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>94000</v>
+        <v>105000</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>100000</v>
+        <v>115000</v>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
@@ -57108,7 +57140,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Seed v1</t>
+          <t>Validated to NL 2026 market (Robert Walters / Robert Half guides + tech pay aggregators)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -57128,7 +57160,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -57267,19 +57299,19 @@
         <v>9</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>66000</v>
+        <v>70000</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>72000</v>
+        <v>78000</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>79000</v>
+        <v>86000</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>86000</v>
+        <v>94000</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>92000</v>
+        <v>102000</v>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
@@ -57288,7 +57320,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Seed v1</t>
+          <t>Validated to NL 2026 market (Robert Walters / Robert Half guides + tech pay aggregators)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -57308,7 +57340,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -57387,19 +57419,19 @@
         <v>3</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>42000</v>
+        <v>48000</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>46000</v>
+        <v>51000</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>49000</v>
+        <v>55000</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>52000</v>
+        <v>58000</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>56000</v>
+        <v>62000</v>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
@@ -57408,7 +57440,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Seed v1</t>
+          <t>Validated to NL 2026 market (Robert Walters / Robert Half guides + tech pay aggregators)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -57428,7 +57460,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
